--- a/Table/Datas/BuffData.xlsx
+++ b/Table/Datas/BuffData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Study\Unreal\ProjectH\Table\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86BA2860-7758-4DC0-BBD6-EF7FB4304D21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C849353-A98C-47DC-84A2-82F3553E0FEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="15">
   <si>
     <t>!Field</t>
     <phoneticPr fontId="4" type="noConversion"/>
@@ -50,10 +50,6 @@
     <t>BuffType</t>
   </si>
   <si>
-    <t>AddATK</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>TurnCount</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -80,6 +76,14 @@
   <si>
     <t>bool</t>
     <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>int</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>AddPATK</t>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -517,16 +521,16 @@
         <v>5</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F4" s="1" t="s">
         <v>7</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
@@ -537,13 +541,13 @@
         <v>5</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>13</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>7</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>4</v>
@@ -554,10 +558,10 @@
         <v>1001</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D6" s="4" t="b">
         <v>0</v>

--- a/Table/Datas/BuffData.xlsx
+++ b/Table/Datas/BuffData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Study\Unreal\ProjectH\Table\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C849353-A98C-47DC-84A2-82F3553E0FEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C819A4D-4CF8-4268-AB8A-0DA989106388}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-27435" yWindow="2085" windowWidth="21600" windowHeight="12570" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -564,7 +564,7 @@
         <v>10</v>
       </c>
       <c r="D6" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E6" s="4">
         <v>3</v>

--- a/Table/Datas/BuffData.xlsx
+++ b/Table/Datas/BuffData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Study\Unreal\ProjectH\Table\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C819A4D-4CF8-4268-AB8A-0DA989106388}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7014FFCB-DAAA-499E-9290-CFB6215D261F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-27435" yWindow="2085" windowWidth="21600" windowHeight="12570" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="16">
   <si>
     <t>!Field</t>
     <phoneticPr fontId="4" type="noConversion"/>
@@ -84,6 +84,10 @@
   <si>
     <t>AddPATK</t>
     <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>MaxStack</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -464,16 +468,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A2:F6"/>
+  <dimension ref="A2:G7"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.5" bestFit="1" customWidth="1"/>
     <col min="2" max="3" width="15" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="15" customWidth="1"/>
-    <col min="5" max="6" width="15" bestFit="1" customWidth="1"/>
+    <col min="5" max="7" width="15" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -492,8 +496,11 @@
       <c r="F2" s="1" t="s">
         <v>0</v>
       </c>
+      <c r="G2" s="1" t="s">
+        <v>0</v>
+      </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -512,8 +519,11 @@
       <c r="F3" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="G3" s="1" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
@@ -527,13 +537,16 @@
         <v>11</v>
       </c>
       <c r="E4" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="G4" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>3</v>
       </c>
@@ -550,10 +563,13 @@
         <v>13</v>
       </c>
       <c r="F5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G5" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="3">
         <v>1001</v>
       </c>
@@ -570,6 +586,32 @@
         <v>3</v>
       </c>
       <c r="F6" s="4">
+        <v>3</v>
+      </c>
+      <c r="G6" s="4">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A7" s="3">
+        <v>1002</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D7" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E7" s="4">
+        <v>1</v>
+      </c>
+      <c r="F7" s="4">
+        <v>3</v>
+      </c>
+      <c r="G7" s="4">
         <v>100</v>
       </c>
     </row>
